--- a/survey_templates/039_school_construction_update_survey--survey_templates.xlsx
+++ b/survey_templates/039_school_construction_update_survey--survey_templates.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -442,7 +442,7 @@
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
     <col width="41" customWidth="1" min="2" max="2"/>
-    <col width="28" customWidth="1" min="3" max="3"/>
+    <col width="41" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -686,7 +686,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Other (please specify)</t>
+          <t>Construction Update Survey Other</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -796,12 +796,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>project_status_other</t>
+          <t>project_status_other_2</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Other (please specify)</t>
+          <t>Project Status Other 2</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -824,7 +824,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Other (please specify)</t>
+          <t>Submission Date Other</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -847,7 +847,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Other (please specify)</t>
+          <t>Submitted By Other</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -893,7 +893,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Other (please specify)</t>
+          <t>School Construction Update Survey Other</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -916,7 +916,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Other (please specify)</t>
+          <t>Submission Time Other</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
@@ -934,12 +934,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>submission_date</t>
+          <t>submission_date_2</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Submission Date</t>
+          <t>Submission Date 2</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
@@ -957,12 +957,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>submitted_by</t>
+          <t>submitted_by_2</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Submitted By</t>
+          <t>Submitted By 2</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
@@ -980,12 +980,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>notes</t>
+          <t>notes_2</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Notes</t>
+          <t>Notes 2</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
@@ -1003,12 +1003,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>comments</t>
+          <t>comments_2</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Comments</t>
+          <t>Comments 2</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
@@ -1026,12 +1026,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>building_name</t>
+          <t>building_name_2</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Building Name</t>
+          <t>Building Name 2</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
@@ -1049,12 +1049,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>project_status</t>
+          <t>project_status_2</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Project Status</t>
+          <t>Project Status 2</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
@@ -1072,12 +1072,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>project_status_other</t>
+          <t>project_status_other_3</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Other (please specify)</t>
+          <t>Project Status Other 3</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
